--- a/Trắc nghiệm ôn luyện/Embedded Software/multiple_choice_sample_template_EMBEDDED_C.xlsx
+++ b/Trắc nghiệm ôn luyện/Embedded Software/multiple_choice_sample_template_EMBEDDED_C.xlsx
@@ -447,7 +447,7 @@
         <v>Trong lập trình C cho hệ thống nhúng, từ khóa volatile được khai báo cho một biến nhằm mục đích gì?</v>
       </c>
       <c r="C2" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D2" t="str">
         <v>Từ khóa volatile buộc trình biên dịch phải đọc giá trị trực tiếp từ ô nhớ RAM/thanh ghi phần cứng mỗi khi biến được gọi, thay vì dùng giá trị lưu tạm trong thanh ghi cache của CPU.</v>
@@ -476,7 +476,7 @@
         <v>Phép toán bitwise nào sau đây được dùng để bật (set) bit thứ 3 của một thanh ghi `reg` lên 1 mà không làm thay đổi các bit khác?</v>
       </c>
       <c r="C3" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D3" t="str">
         <v>Phép OR với bit 1 (`|=`) sẽ đặt bit đó thành 1. `1 &lt;&lt; 3` tạo ra mặt nạ (mask) có bit thứ 3 bằng 1 (0-indexed, tức bit có trọng số 2^3) và các bit khác bằng 0.</v>
@@ -505,7 +505,7 @@
         <v>Phép toán bitwise nào sau đây được dùng để tắt (clear) bit thứ 4 của một thanh ghi `reg` về 0 mà không làm thay đổi các bit khác?</v>
       </c>
       <c r="C4" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D4" t="str">
         <v>Phép AND với bit 0 (`&amp;=`) sẽ đặt bit đó thành 0. Mặt nạ `~(1 &lt;&lt; 4)` có bit thứ 4 bằng 0 và tất cả các bit khác bằng 1, giữ nguyên giá trị các bit còn lại.</v>
@@ -534,7 +534,7 @@
         <v>Trong hệ thống nhúng, bộ nhớ SRAM khác bộ nhớ Flash ở đặc điểm cốt lõi nào?</v>
       </c>
       <c r="C5" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D5" t="str">
         <v>SRAM (Static RAM) có tốc độ truy xuất rất nhanh, dùng lưu RAM runtime (stack/heap/variables). Flash giữ được dữ liệu khi mất nguồn điện, dùng chứa Firmware chương trình.</v>
@@ -563,7 +563,7 @@
         <v>Đoạn code: `const int a = 10;` khai báo cho vi điều khiển. Biến `a` sẽ được trình biên dịch ưu tiên cấp phát vào vùng nhớ nào?</v>
       </c>
       <c r="C6" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D6" t="str">
         <v>Các biến hằng số (const) được lưu trữ trong Flash (Read-Only) để giải phóng không gian bộ nhớ SRAM vốn rất khan hiếm trên các dòng vi điều khiển.</v>
@@ -592,7 +592,7 @@
         <v>Trong ngôn ngữ C, từ khóa static khi khai báo cho một biến toàn cục trong một file source code (`.c`) có tác dụng gì?</v>
       </c>
       <c r="C7" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D7" t="str">
         <v>Static ở mức file (file scope) giúp giới hạn phạm vi hiển thị (visibility) của biến trong file đó, tăng tính đóng gói (encapsulation) và tránh xung đột tên biến khi liên kết dự án.</v>
@@ -621,7 +621,7 @@
         <v>Lỗi "Stack Overflow" (tràn bộ nhớ Stack) trong lập trình nhúng thường xảy ra do nguyên nhân phổ biến nào?</v>
       </c>
       <c r="C8" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D8" t="str">
         <v>Stack lưu trữ địa chỉ trả về của hàm và các biến cục bộ. Gọi đệ quy vô hạn hoặc khai báo mảng lớn trong hàm sẽ nhanh chóng lấp đầy phân vùng Stack, gây sập hệ thống.</v>
@@ -650,7 +650,7 @@
         <v>Trong lập trình nhúng C, kiểu dữ liệu nào sau đây được khuyên dùng để khai báo biến số nguyên 8 bit không dấu để đảm bảo tính nhất quán trên các nền tảng phần cứng khác nhau?</v>
       </c>
       <c r="C9" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D9" t="str">
         <v>Các kiểu dữ liệu như `uint8_t`, `uint16_t`, `uint32_t` trong `&lt;stdint.h&gt;` quy định kích thước bit rõ ràng, giúp code nhúng dễ dàng tương thích chéo giữa các vi điều khiển 8-bit, 16-bit và 32-bit.</v>
@@ -679,7 +679,7 @@
         <v>Cho đoạn mã C nhúng: `uint8_t *ptr = (uint8_t *)0x20000000; *ptr = 0x55;` Đoạn mã này thực hiện hành vi gì?</v>
       </c>
       <c r="C10" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D10" t="str">
         <v>Trong lập trình nhúng, việc ép kiểu số nguyên sang con trỏ cho phép truy cập trực tiếp vào các địa chỉ phần cứng cố định (như địa chỉ RAM hoặc địa chỉ thanh ghi ngoại vi).</v>
@@ -708,7 +708,7 @@
         <v>Trong hệ điều hành thời gian thực (RTOS) cho vi điều khiển, sự khác biệt cơ bản giữa Mutex và Semaphore là gì?</v>
       </c>
       <c r="C11" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D11" t="str">
         <v>Mutex (Mutual Exclusion) hoạt động như một chiếc khóa chỉ người giữ khóa mới mở được. Nó hỗ trợ Priority Inheritance để tránh lỗi Priority Inversion. Semaphore được giải phóng bởi bất kỳ task nào.</v>
@@ -737,7 +737,7 @@
         <v>Từ khóa `static` khi khai báo cho một biến cục bộ bên trong một hàm (local variable) có tác dụng gì?</v>
       </c>
       <c r="C12" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D12" t="str">
         <v>Biến cục bộ static duy trì trạng thái của nó qua các lần gọi hàm, rất hữu ích khi cần đếm số lần gọi hàm hoặc lưu trữ trạng thái của một máy trạng thái (state machine) nội bộ hàm.</v>
@@ -766,7 +766,7 @@
         <v>Khi biên dịch mã nguồn C nhúng, hành vi "Structure Padding" (đệm cấu trúc) của trình biên dịch có thể gây ra ảnh hưởng gì lớn nhất đối với tài nguyên của vi điều khiển?</v>
       </c>
       <c r="C13" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D13" t="str">
         <v>Trình biên dịch tự động thêm bytes đệm để căn lề địa chỉ biến (ví dụ biến 32-bit bắt buộc nằm ở địa chỉ chia hết cho 4). Để tránh padding tốn RAM khi truyền nhận dữ liệu, ta dùng thuộc tính `__attribute__((packed))`.</v>
@@ -795,7 +795,7 @@
         <v>Tại sao việc lạm dụng cấp phát bộ nhớ động bằng hàm `malloc()` và `free()` thường bị hạn chế hoặc cấm kỵ trong các hệ thống nhúng thời gian thực (RTOS) quan trọng?</v>
       </c>
       <c r="C14" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D14" t="str">
         <v>Phân mảnh bộ nhớ có thể khiến hệ thống sập vì không tìm được khối nhớ liên tục đủ lớn. Hơn nữa, việc tìm kiếm khối nhớ trống của malloc mất thời gian thay đổi tùy theo trạng thái Heap, vi phạm tính thời gian thực (real-time).</v>
@@ -824,7 +824,7 @@
         <v>Cho đoạn mã: `#define SET_BIT(reg, bit) (reg |= (1 &lt;&lt; bit))`. Điểm cần lưu ý nhất khi sử dụng macro kiểu này trong lập trình C nhúng là gì?</v>
       </c>
       <c r="C15" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D15" t="str">
         <v>Macro là phép thay thế chuỗi thuần túy trước khi biên dịch (preprocessor). Nếu không đóng ngoặc các tham số, việc truyền biểu thức như `SET_BIT(my_reg, 1 + 2)` sẽ bị dịch sai thứ tự toán tử.</v>
@@ -853,7 +853,7 @@
         <v>Trong lập trình C nhúng, tác dụng của việc khai báo thuộc tính `__attribute__((packed))` cho một struct là gì?</v>
       </c>
       <c r="C16" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D16" t="str">
         <v>Packed struct giúp kích thước struct bằng đúng tổng kích thước các trường thành phần, rất quan trọng khi định nghĩa các gói tin truyền thông (như frame UART/SPI) để gửi nhận dữ liệu thô trực tiếp.</v>
@@ -882,7 +882,7 @@
         <v>Tại sao các biến được chia sẻ chung giữa một hàm phục vụ ngắt (ISR) và luồng chương trình chính (main loop) bắt buộc phải được khai báo với từ khóa `volatile`?</v>
       </c>
       <c r="C17" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D17" t="str">
         <v>Nếu không dùng `volatile`, trình biên dịch phân tích luồng code thấy `main` không sửa biến đó sẽ cất giá trị biến vào thanh ghi để chạy nhanh, không nhận biết được biến đã bị ngắt (luồng phần cứng bên ngoài) thay đổi giá trị trong RAM.</v>
@@ -911,7 +911,7 @@
         <v>Một vi điều khiển 32-bit có bus dữ liệu và bus địa chỉ 32-bit. Con trỏ (pointer) khai báo trên hệ thống này sẽ chiếm bao nhiêu byte bộ nhớ?</v>
       </c>
       <c r="C18" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D18" t="str">
         <v>Kích thước con trỏ chỉ phụ thuộc vào kiến trúc địa chỉ của hệ thống (bus địa chỉ). Trên hệ thống 32-bit là 4 bytes, hệ thống 64-bit là 8 bytes, hệ thống 8-bit (như PIC/AVR) là 1 hoặc 2 bytes.</v>
@@ -940,7 +940,7 @@
         <v>Cho đoạn mã C nhúng: `#define REG_ADDR 0x40021000 \n #define REG_VAL (*(volatile uint32_t *)REG_ADDR)`. Tại sao việc ép kiểu con trỏ ở đây bắt buộc phải có cả từ khóa `volatile` và kiểu `uint32_t`?</v>
       </c>
       <c r="C19" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D19" t="str">
         <v>Ghi vào thanh ghi phần cứng (như bật đèn LED) thường không có luồng đọc lại trong code. Trình biên dịch có thể coi lệnh ghi này là thừa và tối ưu xóa bỏ nếu thiếu `volatile`. `uint32_t` kích hoạt lệnh truy cập bộ nhớ 32-bit (như LDR/STR trong ARM).</v>
@@ -969,7 +969,7 @@
         <v>Trong thiết kế phần mềm nhúng sử dụng RTOS, hiện tượng "Priority Inversion" (nghịch đảo độ ưu tiên) xảy ra trong điều kiện nào và cách giải quyết?</v>
       </c>
       <c r="C20" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D20" t="str">
         <v>Priority Inheritance giải quyết bằng cách tạm thời nâng độ ưu tiên của Task thấp (đang giữ tài nguyên) lên bằng độ ưu tiên của Task cao đang chờ, giúp Task thấp chạy nhanh giải phóng tài nguyên, ngăn Task trung bình chiếm quyền.</v>
@@ -998,7 +998,7 @@
         <v>Cho đoạn mã C: `uint32_t *p = (uint32_t *)0x20000001; uint32_t val = *p;` Khi chạy trên một MCU kiến trúc ARM Cortex-M0, hiện tượng gì sẽ xảy ra?</v>
       </c>
       <c r="C21" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D21" t="str">
         <v>ARM Cortex-M0 không hỗ trợ Unaligned Access cho các lệnh đọc ghi 32-bit. Việc truy cập địa chỉ lẻ không chia hết cho 4 sẽ kích hoạt lỗi phần cứng HardFault lập tức.</v>
@@ -1027,7 +1027,7 @@
         <v>Lập trình viên viết hàm ISR để nhận dữ liệu từ UART: `void UART_ISR() { uint8_t data = UART-&gt;DR; printf("Recv: %d\n", data); }` Hãy chỉ ra lỗi nghiêm trọng nhất của hàm này.</v>
       </c>
       <c r="C22" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D22" t="str">
         <v>printf thực thi rất lâu do phải định dạng chuỗi và gửi đi qua cổng debug. Trong khi đó, UART nhận dữ liệu liên tục. Hàm ISR chạy quá lâu sẽ khiến CPU không kịp xử lý ngắt nhận tiếp theo, gây Overrun.</v>
@@ -1056,7 +1056,7 @@
         <v>Làm thế nào để triển khai một cấu trúc hàng đợi vòng tròn (Ring Buffer / Circular Queue) an toàn luồng (Thread-safe) giữa một ngắt ISR (chỉ ghi dữ liệu) và luồng chính main (chỉ đọc dữ liệu) mà không cần tắt ngắt?</v>
       </c>
       <c r="C23" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D23" t="str">
         <v>Nếu luồng chính chỉ đọc và cập nhật chỉ mục Read, ngắt chỉ ghi và cập nhật Write, các thao tác này hoàn toàn độc lập và không chồng lấn. Khai báo volatile đảm bảo CPU đọc giá trị cập nhật tức thì, giúp giao tiếp an toàn không cần khóa ngắt.</v>
@@ -1085,7 +1085,7 @@
         <v>Trong các hệ thống nhúng siêu tiết kiệm năng lượng (Ultra-low power), BA/Embedded Dev giải quyết bài toán giữ lại nội dung biến trong bộ nhớ RAM khi vi điều khiển vào chế độ Deep Sleep như thế nào?</v>
       </c>
       <c r="C24" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D24" t="str">
         <v>Trong chế độ ngủ sâu (Deep Sleep/Power-down), toàn bộ nguồn cấp cho lõi CPU và SRAM thông thường bị ngắt để tiết kiệm điện. Chỉ có vùng RAM duy trì (Retention RAM) hoặc bộ nhớ Flash/EEPROM mới giữ lại được dữ liệu.</v>
@@ -1114,7 +1114,7 @@
         <v>Để phát hiện và sửa các lỗi rò rỉ bộ nhớ (Memory Leak) và lỗi sử dụng con trỏ hoang (Wild/Dangling Pointer) trong hệ thống nhúng chạy bare-metal (không có OS), kỹ thuật nào hiệu quả nhất?</v>
       </c>
       <c r="C25" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D25" t="str">
         <v>Hệ thống nhúng nhỏ không chạy được các công cụ nặng như Valgrind. Việc tự viết Custom Allocator (ghi đè malloc/free) ghi lại siêu dữ liệu (metadata) giúp theo dõi bộ nhớ rò rỉ rất hiệu quả.</v>
@@ -1143,7 +1143,7 @@
         <v>Cho định nghĩa: `typedef void (*callback_t)(uint8_t);`. Biểu thức này khai báo loại cấu trúc dữ liệu nào trong C và có ứng dụng gì trong phần mềm nhúng?</v>
       </c>
       <c r="C26" t="str">
-        <v>Embedded C</v>
+        <v>Embedded C Programming</v>
       </c>
       <c r="D26" t="str">
         <v>Con trỏ hàm (Function Pointer) là kỹ thuật quan trọng trong lập trình nhúng để thiết lập các thư viện Driver phần cứng (ví dụ: đăng ký hàm Callback xử lý khi nhận được byte UART).</v>

--- a/Trắc nghiệm ôn luyện/Embedded Software/multiple_choice_sample_template_EMBEDDED_C.xlsx
+++ b/Trắc nghiệm ôn luyện/Embedded Software/multiple_choice_sample_template_EMBEDDED_C.xlsx
@@ -453,19 +453,19 @@
         <v>Từ khóa volatile buộc trình biên dịch phải đọc giá trị trực tiếp từ ô nhớ RAM/thanh ghi phần cứng mỗi khi biến được gọi, thay vì dùng giá trị lưu tạm trong thanh ghi cache của CPU.</v>
       </c>
       <c r="E2" t="str">
+        <v>Yêu cầu trình biên dịch cấp phát biến này trực tiếp vào bộ nhớ Flash thay vì bộ nhớ RAM để tiết kiệm dung lượng</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Tăng tốc độ truy xuất của biến bằng cách lưu trữ nó cố định trong thanh ghi đa dụng của CPU</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Ngăn chặn các luồng chương trình khác chỉnh sửa giá trị của biến này — làm biến thành hằng số</v>
+      </c>
+      <c r="H2" t="str">
         <v>Báo cho trình biên dịch không được tối ưu hóa biến này; giá trị của nó có thể thay đổi bất kỳ lúc nào ngoài tầm kiểm soát của luồng chương trình chính (như do ngắt hoặc thanh ghi ngoại vi)</v>
       </c>
-      <c r="F2" t="str">
-        <v>Yêu cầu trình biên dịch cấp phát biến này trực tiếp vào bộ nhớ Flash thay vì bộ nhớ RAM để tiết kiệm dung lượng</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Tăng tốc độ truy xuất của biến bằng cách lưu trữ nó cố định trong thanh ghi đa dụng của CPU</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Ngăn chặn các luồng chương trình khác chỉnh sửa giá trị của biến này — làm biến thành hằng số</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Phép OR với bit 1 (`|=`) sẽ đặt bit đó thành 1. `1 &lt;&lt; 3` tạo ra mặt nạ (mask) có bit thứ 3 bằng 1 (0-indexed, tức bit có trọng số 2^3) và các bit khác bằng 0.</v>
       </c>
       <c r="E3" t="str">
+        <v>reg &amp;= ~(1 &lt;&lt; 3) — thực hiện phép toán AND với phủ định của mặt nạ dịch bit</v>
+      </c>
+      <c r="F3" t="str">
+        <v>reg = (1 &lt;&lt; 3) — gán trực tiếp giá trị mới cho toàn bộ thanh ghi</v>
+      </c>
+      <c r="G3" t="str">
         <v>reg |= (1 &lt;&lt; 3) — thực hiện phép toán OR bitwise với mặt nạ dịch bit</v>
       </c>
-      <c r="F3" t="str">
-        <v>reg &amp;= ~(1 &lt;&lt; 3) — thực hiện phép toán AND với phủ định của mặt nạ dịch bit</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>reg ^= (1 &lt;&lt; 3) — thực hiện phép toán XOR bitwise để đảo bit</v>
       </c>
-      <c r="H3" t="str">
-        <v>reg = (1 &lt;&lt; 3) — gán trực tiếp giá trị mới cho toàn bộ thanh ghi</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>Phép AND với bit 0 (`&amp;=`) sẽ đặt bit đó thành 0. Mặt nạ `~(1 &lt;&lt; 4)` có bit thứ 4 bằng 0 và tất cả các bit khác bằng 1, giữ nguyên giá trị các bit còn lại.</v>
       </c>
       <c r="E4" t="str">
+        <v>reg = ~(1 &lt;&lt; 4) — gán trực tiếp đảo mặt nạ cho toàn bộ thanh ghi</v>
+      </c>
+      <c r="F4" t="str">
         <v>reg &amp;= ~(1 &lt;&lt; 4) — thực hiện phép toán AND bitwise với đảo mặt nạ dịch bit</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>reg |= (1 &lt;&lt; 4) — thực hiện phép toán OR bitwise với mặt nạ dịch bit</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>reg ^= (1 &lt;&lt; 4) — thực hiện phép toán XOR bitwise để đảo bit</v>
       </c>
-      <c r="H4" t="str">
-        <v>reg = ~(1 &lt;&lt; 4) — gán trực tiếp đảo mặt nạ cho toàn bộ thanh ghi</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>SRAM (Static RAM) có tốc độ truy xuất rất nhanh, dùng lưu RAM runtime (stack/heap/variables). Flash giữ được dữ liệu khi mất nguồn điện, dùng chứa Firmware chương trình.</v>
       </c>
       <c r="E5" t="str">
+        <v>SRAM chỉ cho phép đọc dữ liệu; Flash cho phép cả đọc và ghi dữ liệu ở tốc độ cao</v>
+      </c>
+      <c r="F5" t="str">
+        <v>SRAM được tích hợp trên các mạch ngoại vi bên ngoài; Flash luôn tích hợp sẵn trong nhân CPU</v>
+      </c>
+      <c r="G5" t="str">
         <v>SRAM là bộ nhớ bay hơi (mất dữ liệu khi mất điện) dùng lưu biến tạm; Flash là bộ nhớ không bay hơi dùng lưu mã nguồn chương trình và dữ liệu tĩnh</v>
       </c>
-      <c r="F5" t="str">
+      <c r="H5" t="str">
         <v>SRAM có dung lượng lớn hơn Flash gấp nhiều lần trên cùng một dòng vi điều khiển</v>
       </c>
-      <c r="G5" t="str">
-        <v>SRAM chỉ cho phép đọc dữ liệu; Flash cho phép cả đọc và ghi dữ liệu ở tốc độ cao</v>
-      </c>
-      <c r="H5" t="str">
-        <v>SRAM được tích hợp trên các mạch ngoại vi bên ngoài; Flash luôn tích hợp sẵn trong nhân CPU</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>Các biến hằng số (const) được lưu trữ trong Flash (Read-Only) để giải phóng không gian bộ nhớ SRAM vốn rất khan hiếm trên các dòng vi điều khiển.</v>
       </c>
       <c r="E6" t="str">
+        <v>Bộ nhớ SRAM vùng Heap — cấp phát động cho biến khi chương trình chạy</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Bộ nhớ SRAM vùng Stack — cấp phát cục bộ cho các biến tạm thời trong hàm</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Vùng nhớ thanh ghi của CPU — để tăng tốc độ tính toán trực tiếp</v>
+      </c>
+      <c r="H6" t="str">
         <v>Bộ nhớ Flash (hoặc ROM) — vì const khai báo hằng số không đổi, giúp tiết kiệm bộ nhớ RAM giới hạn của MCU</v>
       </c>
-      <c r="F6" t="str">
-        <v>Bộ nhớ SRAM vùng Heap — cấp phát động cho biến khi chương trình chạy</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Bộ nhớ SRAM vùng Stack — cấp phát cục bộ cho các biến tạm thời trong hàm</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Vùng nhớ thanh ghi của CPU — để tăng tốc độ tính toán trực tiếp</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Static ở mức file (file scope) giúp giới hạn phạm vi hiển thị (visibility) của biến trong file đó, tăng tính đóng gói (encapsulation) và tránh xung đột tên biến khi liên kết dự án.</v>
       </c>
       <c r="E7" t="str">
+        <v>Giữ nguyên giá trị của biến qua các lần gọi hàm và lưu biến vào bộ nhớ Stack</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Báo cho trình biên dịch biết biến này là hằng số và không được phép chỉnh sửa giá trị</v>
+      </c>
+      <c r="G7" t="str">
         <v>Giới hạn phạm vi truy cập của biến đó chỉ trong file `.c` khai báo; các file khác không thể truy cập bằng từ khóa `extern`</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Giữ nguyên giá trị của biến qua các lần gọi hàm và lưu biến vào bộ nhớ Stack</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Báo cho trình biên dịch biết biến này là hằng số và không được phép chỉnh sửa giá trị</v>
       </c>
       <c r="H7" t="str">
         <v>Tự động giải phóng biến khỏi bộ nhớ RAM ngay khi kết thúc hàm main</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Stack lưu trữ địa chỉ trả về của hàm và các biến cục bộ. Gọi đệ quy vô hạn hoặc khai báo mảng lớn trong hàm sẽ nhanh chóng lấp đầy phân vùng Stack, gây sập hệ thống.</v>
       </c>
       <c r="E8" t="str">
+        <v>Biên dịch chương trình ở chế độ Release thay vì chế độ Debug thông thường</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Kết nối nguồn điện cấp cho vi điều khiển bị sụt áp đột ngột khi chạy động cơ</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Sử dụng quá nhiều câu lệnh cấp phát bộ nhớ động bằng hàm `malloc()` mà quên giải phóng bằng `free()`</v>
+      </c>
+      <c r="H8" t="str">
         <v>Gọi đệ quy quá sâu hoặc khai báo các mảng/biến cục bộ có kích thước quá lớn vượt quá dung lượng Stack được cấu hình</v>
       </c>
-      <c r="F8" t="str">
-        <v>Sử dụng quá nhiều câu lệnh cấp phát bộ nhớ động bằng hàm `malloc()` mà quên giải phóng bằng `free()`</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Kết nối nguồn điện cấp cho vi điều khiển bị sụt áp đột ngột khi chạy động cơ</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Biên dịch chương trình ở chế độ Release thay vì chế độ Debug thông thường</v>
-      </c>
       <c r="I8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>Các kiểu dữ liệu như `uint8_t`, `uint16_t`, `uint32_t` trong `&lt;stdint.h&gt;` quy định kích thước bit rõ ràng, giúp code nhúng dễ dàng tương thích chéo giữa các vi điều khiển 8-bit, 16-bit và 32-bit.</v>
       </c>
       <c r="E9" t="str">
-        <v>uint8_t — định nghĩa trong thư viện chuẩn &lt;stdint.h&gt; đảm bảo chính xác 8 bit không dấu</v>
+        <v>int8_t — kiểu số nguyên 8 bit có dấu</v>
       </c>
       <c r="F9" t="str">
         <v>unsigned char — kiểu ký tự không dấu có độ dài phụ thuộc vào trình biên dịch</v>
       </c>
       <c r="G9" t="str">
-        <v>int8_t — kiểu số nguyên 8 bit có dấu</v>
+        <v>unsigned int — kiểu số nguyên không dấu có độ dài thường là 16 hoặc 32 bit</v>
       </c>
       <c r="H9" t="str">
-        <v>unsigned int — kiểu số nguyên không dấu có độ dài thường là 16 hoặc 32 bit</v>
+        <v>uint8_t — định nghĩa trong thư viện chuẩn &lt;stdint.h&gt; đảm bảo chính xác 8 bit không dấu</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -714,19 +714,19 @@
         <v>Mutex (Mutual Exclusion) hoạt động như một chiếc khóa chỉ người giữ khóa mới mở được. Nó hỗ trợ Priority Inheritance để tránh lỗi Priority Inversion. Semaphore được giải phóng bởi bất kỳ task nào.</v>
       </c>
       <c r="E11" t="str">
+        <v>Mutex có tốc độ xử lý chậm hơn Semaphore gấp nhiều lần do tốn bộ nhớ RAM</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Mutex là tính năng phần cứng; Semaphore là tính năng phần mềm của vi điều khiển</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Mutex chỉ chạy được trên hệ thống đa nhân; Semaphore chạy được trên hệ thống đơn nhân</v>
+      </c>
+      <c r="H11" t="str">
         <v>Mutex có cơ chế sở hữu (ownership) và hỗ trợ giao thức tránh nghịch đảo độ ưu tiên; Semaphore không có quyền sở hữu, dùng để đồng bộ hóa hoặc đếm tài nguyên</v>
       </c>
-      <c r="F11" t="str">
-        <v>Mutex chỉ chạy được trên hệ thống đa nhân; Semaphore chạy được trên hệ thống đơn nhân</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Mutex có tốc độ xử lý chậm hơn Semaphore gấp nhiều lần do tốn bộ nhớ RAM</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Mutex là tính năng phần cứng; Semaphore là tính năng phần mềm của vi điều khiển</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -746,13 +746,13 @@
         <v>Biến sẽ giữ lại giá trị của nó qua các lần gọi hàm khác nhau, chỉ được khởi tạo một lần duy nhất khi bắt đầu chương trình và lưu ở vùng RAM tĩnh thay vì Stack</v>
       </c>
       <c r="F12" t="str">
+        <v>Biến sẽ tự động bị xóa khỏi bộ nhớ RAM ngay khi hàm kết thúc thực thi để giải phóng bộ nhớ</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Biến được lưu trữ cố định ở bộ nhớ Flash giống như khai báo từ khóa `const`</v>
+      </c>
+      <c r="H12" t="str">
         <v>Biến sẽ không cho phép các hàm ở file nguồn khác sửa đổi giá trị thông qua từ khóa `extern`</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Biến sẽ tự động bị xóa khỏi bộ nhớ RAM ngay khi hàm kết thúc thực thi để giải phóng bộ nhớ</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Biến được lưu trữ cố định ở bộ nhớ Flash giống như khai báo từ khóa `const`</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -778,10 +778,10 @@
         <v>Làm chương trình bị lỗi cú pháp không thể biên dịch thành công</v>
       </c>
       <c r="G13" t="str">
+        <v>Gây lỗi tràn bộ nhớ Flash khi nạp chương trình vào vi điều khiển</v>
+      </c>
+      <c r="H13" t="str">
         <v>Làm chậm đáng kể tốc độ tính toán số thực của nhân xử lý CPU</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Gây lỗi tràn bộ nhớ Flash khi nạp chương trình vào vi điều khiển</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -801,19 +801,19 @@
         <v>Phân mảnh bộ nhớ có thể khiến hệ thống sập vì không tìm được khối nhớ liên tục đủ lớn. Hơn nữa, việc tìm kiếm khối nhớ trống của malloc mất thời gian thay đổi tùy theo trạng thái Heap, vi phạm tính thời gian thực (real-time).</v>
       </c>
       <c r="E14" t="str">
+        <v>Hàm `malloc()` không thể chạy được trên các dòng vi điều khiển 32-bit ARM Cortex-M</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Cấp phát động làm tiêu tốn dung lượng bộ nhớ Flash của vi điều khiển gấp nhiều lần</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Làm tăng đáng kể dòng tiêu thụ điện năng của vi điều khiển ở chế độ hoạt động bình thường</v>
+      </c>
+      <c r="H14" t="str">
         <v>Gây ra hiện tượng phân mảnh bộ nhớ (Memory Fragmentation) dẫn đến lỗi cấp phát thất bại sau một thời gian chạy, và thời gian thực thi hàm không xác định (non-deterministic)</v>
       </c>
-      <c r="F14" t="str">
-        <v>Hàm `malloc()` không thể chạy được trên các dòng vi điều khiển 32-bit ARM Cortex-M</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Cấp phát động làm tiêu tốn dung lượng bộ nhớ Flash của vi điều khiển gấp nhiều lần</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Làm tăng đáng kể dòng tiêu thụ điện năng của vi điều khiển ở chế độ hoạt động bình thường</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -859,19 +859,19 @@
         <v>Packed struct giúp kích thước struct bằng đúng tổng kích thước các trường thành phần, rất quan trọng khi định nghĩa các gói tin truyền thông (như frame UART/SPI) để gửi nhận dữ liệu thô trực tiếp.</v>
       </c>
       <c r="E16" t="str">
+        <v>Tự động mã hóa toàn bộ nội dung của struct khi lưu vào bộ nhớ Flash để bảo mật thông tin</v>
+      </c>
+      <c r="F16" t="str">
         <v>Yêu cầu trình biên dịch loại bỏ toàn bộ các byte đệm (Structure Padding), sắp xếp các trường dữ liệu liền sát nhau để tối ưu dung lượng và phục vụ truyền nhận dữ liệu thô</v>
       </c>
-      <c r="F16" t="str">
-        <v>Tự động mã hóa toàn bộ nội dung của struct khi lưu vào bộ nhớ Flash để bảo mật thông tin</v>
-      </c>
       <c r="G16" t="str">
+        <v>Tự động tạo ra các hàm getter/setter tương ứng cho các trường trong struct giống như OOP</v>
+      </c>
+      <c r="H16" t="str">
         <v>Cho phép struct đó được lưu trữ trực tiếp trong các thanh ghi đa dụng của CPU</v>
       </c>
-      <c r="H16" t="str">
-        <v>Tự động tạo ra các hàm getter/setter tương ứng cho các trường trong struct giống như OOP</v>
-      </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Nếu không dùng `volatile`, trình biên dịch phân tích luồng code thấy `main` không sửa biến đó sẽ cất giá trị biến vào thanh ghi để chạy nhanh, không nhận biết được biến đã bị ngắt (luồng phần cứng bên ngoài) thay đổi giá trị trong RAM.</v>
       </c>
       <c r="E17" t="str">
+        <v>Để tự động khóa luồng chương trình chính khi ngắt đang ghi dữ liệu vào biến đó</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Để lưu biến đó vào bộ nhớ Flash nhằm tránh mất dữ liệu khi vi điều khiển reset</v>
+      </c>
+      <c r="G17" t="str">
         <v>Để ngăn trình biên dịch tối ưu hóa cất biến vào thanh ghi, đảm bảo CPU luôn đọc giá trị mới nhất từ ô nhớ RAM do ngắt có thể cập nhật biến bất kỳ lúc nào</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Để tự động khóa luồng chương trình chính khi ngắt đang ghi dữ liệu vào biến đó</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Để lưu biến đó vào bộ nhớ Flash nhằm tránh mất dữ liệu khi vi điều khiển reset</v>
       </c>
       <c r="H17" t="str">
         <v>Để cho phép biến đó được khai báo với kiểu dữ liệu số thực có độ chính xác kép (double)</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Kích thước con trỏ chỉ phụ thuộc vào kiến trúc địa chỉ của hệ thống (bus địa chỉ). Trên hệ thống 32-bit là 4 bytes, hệ thống 64-bit là 8 bytes, hệ thống 8-bit (như PIC/AVR) là 1 hoặc 2 bytes.</v>
       </c>
       <c r="E18" t="str">
+        <v>2 bytes — vì địa chỉ bộ nhớ vi điều khiển thường nhỏ hơn địa chỉ trên máy tính cá nhân</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Tùy thuộc vào kiểu dữ liệu mà con trỏ trỏ tới (ví dụ: con trỏ char chiếm 1 byte, con trỏ int chiếm 4 bytes)</v>
+      </c>
+      <c r="G18" t="str">
         <v>4 bytes — vì con trỏ lưu trữ địa chỉ bộ nhớ, và địa chỉ trên kiến trúc 32-bit dài đúng 32 bit (4 bytes)</v>
       </c>
-      <c r="F18" t="str">
-        <v>2 bytes — vì địa chỉ bộ nhớ vi điều khiển thường nhỏ hơn địa chỉ trên máy tính cá nhân</v>
-      </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>8 bytes — độ dài chuẩn cho mọi con trỏ trong ngôn ngữ lập trình C hiện đại</v>
       </c>
-      <c r="H18" t="str">
-        <v>Tùy thuộc vào kiểu dữ liệu mà con trỏ trỏ tới (ví dụ: con trỏ char chiếm 1 byte, con trỏ int chiếm 4 bytes)</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -949,13 +949,13 @@
         <v>`volatile` ngăn chặn trình biên dịch tối ưu xóa bỏ các lệnh ghi/đọc thanh ghi phần cứng ảo; `uint32_t` đảm bảo CPU truy xuất đúng thanh ghi 32-bit tránh lỗi lệch địa chỉ (alignment)</v>
       </c>
       <c r="F19" t="str">
+        <v>Đây là cú pháp mặc định của thư viện C, không ảnh hưởng đến mã máy khi biên dịch thực tế</v>
+      </c>
+      <c r="G19" t="str">
         <v>`volatile` dùng để mã hóa địa chỉ 0x40021000 tránh bị tin tặc hack; `uint32_t` dùng để tăng tốc độ ghi dữ liệu</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>`volatile` bắt buộc phải có để báo cho CPU biết đây là địa chỉ bộ nhớ Flash; `uint32_t` khai báo biến số thực</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Đây là cú pháp mặc định của thư viện C, không ảnh hưởng đến mã máy khi biên dịch thực tế</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -975,19 +975,19 @@
         <v>Priority Inheritance giải quyết bằng cách tạm thời nâng độ ưu tiên của Task thấp (đang giữ tài nguyên) lên bằng độ ưu tiên của Task cao đang chờ, giúp Task thấp chạy nhanh giải phóng tài nguyên, ngăn Task trung bình chiếm quyền.</v>
       </c>
       <c r="E20" t="str">
+        <v>Độ ưu tiên của các Task bị đảo ngược một cách ngẫu nhiên khi bộ nhớ RAM bị tràn dữ liệu. Giải pháp: Thiết lập lại cấu hình vùng nhớ Stack</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Task có độ ưu tiên thấp chạy nhanh hơn Task có độ ưu tiên cao do dùng ít biến. Giải pháp: Thêm các hàm delay vào Task thấp</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Hệ thống ngắt hoạt động đè lên quyền điều phối của nhân RTOS. Giải pháp: Tắt toàn bộ ngắt trong suốt quá trình chạy RTOS</v>
+      </c>
+      <c r="H20" t="str">
         <v>Task ưu tiên cao bị chặn bởi Task ưu tiên trung bình do Task ưu tiên thấp đang giữ Mutex/tài nguyên mà Task cao cần. Giải pháp: Sử dụng cơ chế Kế thừa độ ưu tiên (Priority Inheritance)</v>
       </c>
-      <c r="F20" t="str">
-        <v>Độ ưu tiên của các Task bị đảo ngược một cách ngẫu nhiên khi bộ nhớ RAM bị tràn dữ liệu. Giải pháp: Thiết lập lại cấu hình vùng nhớ Stack</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Task có độ ưu tiên thấp chạy nhanh hơn Task có độ ưu tiên cao do dùng ít biến. Giải pháp: Thêm các hàm delay vào Task thấp</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Hệ thống ngắt hoạt động đè lên quyền điều phối của nhân RTOS. Giải pháp: Tắt toàn bộ ngắt trong suốt quá trình chạy RTOS</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1004,10 +1004,10 @@
         <v>ARM Cortex-M0 không hỗ trợ Unaligned Access cho các lệnh đọc ghi 32-bit. Việc truy cập địa chỉ lẻ không chia hết cho 4 sẽ kích hoạt lỗi phần cứng HardFault lập tức.</v>
       </c>
       <c r="E21" t="str">
+        <v>Giá trị biến val sẽ tự động được làm tròn về địa chỉ 0x20000000 để đọc dữ liệu</v>
+      </c>
+      <c r="F21" t="str">
         <v>Hệ thống phát sinh ngoại lệ phần cứng (HardFault Exception) do truy cập bộ nhớ không căn lề (Unaligned Memory Access) — địa chỉ 0x20000001 không chia hết cho 4</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Giá trị biến val sẽ tự động được làm tròn về địa chỉ 0x20000000 để đọc dữ liệu</v>
       </c>
       <c r="G21" t="str">
         <v>Đoạn code chạy bình thường nhưng giá trị đọc được bị đảo ngược thứ tự các byte (Little Endian)</v>
@@ -1016,7 +1016,7 @@
         <v>Trình biên dịch báo lỗi cú pháp ngay lập tức và không cho phép tạo file hex nạp vào chip</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>printf thực thi rất lâu do phải định dạng chuỗi và gửi đi qua cổng debug. Trong khi đó, UART nhận dữ liệu liên tục. Hàm ISR chạy quá lâu sẽ khiến CPU không kịp xử lý ngắt nhận tiếp theo, gây Overrun.</v>
       </c>
       <c r="E22" t="str">
-        <v>Sử dụng hàm `printf()` trong ISR — đây là hàm tốn thời gian, có thể gây blocking/nghẽn luồng và làm mất các byte dữ liệu tiếp theo của UART do tràn bộ đệm phần cứng (Overrun Error)</v>
+        <v>Không tắt ngắt toàn cục trước khi thực hiện việc đọc thanh ghi dữ liệu UART-&gt;DR</v>
       </c>
       <c r="F22" t="str">
         <v>Lưu dữ liệu vào biến cục bộ `data` thay vì biến static hoặc toàn cục</v>
       </c>
       <c r="G22" t="str">
-        <v>Không tắt ngắt toàn cục trước khi thực hiện việc đọc thanh ghi dữ liệu UART-&gt;DR</v>
+        <v>Thiếu kiểu trả về của hàm ISR bắt buộc phải là kiểu con trỏ dữ liệu</v>
       </c>
       <c r="H22" t="str">
-        <v>Thiếu kiểu trả về của hàm ISR bắt buộc phải là kiểu con trỏ dữ liệu</v>
+        <v>Sử dụng hàm `printf()` trong ISR — đây là hàm tốn thời gian, có thể gây blocking/nghẽn luồng và làm mất các byte dữ liệu tiếp theo của UART do tràn bộ đệm phần cứng (Overrun Error)</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Nếu luồng chính chỉ đọc và cập nhật chỉ mục Read, ngắt chỉ ghi và cập nhật Write, các thao tác này hoàn toàn độc lập và không chồng lấn. Khai báo volatile đảm bảo CPU đọc giá trị cập nhật tức thì, giúp giao tiếp an toàn không cần khóa ngắt.</v>
       </c>
       <c r="E23" t="str">
+        <v>Sử dụng biến cờ hiệu kiểu boolean và yêu cầu luồng chính thực hiện vòng lặp vô hạn kiểm tra cờ hiệu</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Tắt ngắt toàn cục mỗi khi luồng chính cần đọc dữ liệu từ Ring Buffer</v>
+      </c>
+      <c r="G23" t="str">
         <v>Sử dụng các biến chỉ mục Write và Read khai báo `volatile`, đảm bảo các thao tác cập nhật chỉ mục là nguyên tử (atomic) và chỉ có luồng chính cập nhật Read, ngắt cập nhật Write</v>
       </c>
-      <c r="F23" t="str">
-        <v>Sử dụng biến cờ hiệu kiểu boolean và yêu cầu luồng chính thực hiện vòng lặp vô hạn kiểm tra cờ hiệu</v>
-      </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Sử dụng hàm cấp phát động `realloc()` để thay đổi kích thước buffer mỗi khi ngắt xảy ra</v>
       </c>
-      <c r="H23" t="str">
-        <v>Tắt ngắt toàn cục mỗi khi luồng chính cần đọc dữ liệu từ Ring Buffer</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Trong chế độ ngủ sâu (Deep Sleep/Power-down), toàn bộ nguồn cấp cho lõi CPU và SRAM thông thường bị ngắt để tiết kiệm điện. Chỉ có vùng RAM duy trì (Retention RAM) hoặc bộ nhớ Flash/EEPROM mới giữ lại được dữ liệu.</v>
       </c>
       <c r="E24" t="str">
+        <v>Khai báo tất cả các biến cần lưu trữ với từ khóa hằng số `const`</v>
+      </c>
+      <c r="F24" t="str">
         <v>Sử dụng vùng RAM đặc biệt (Backup RAM/SRAM retention) được cấp nguồn điện duy trì riêng biệt, hoặc sao lưu các biến quan trọng vào bộ nhớ EEPROM/Flash trước khi ngủ</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>Không cần làm gì vì bộ nhớ SRAM thông thường luôn giữ được dữ liệu mà không cần tiêu tốn năng lượng điện</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v>Sử dụng tụ điện dung lượng cực lớn đấu song song với từng ô nhớ của bộ nhớ RAM</v>
       </c>
-      <c r="H24" t="str">
-        <v>Khai báo tất cả các biến cần lưu trữ với từ khóa hằng số `const`</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Hệ thống nhúng nhỏ không chạy được các công cụ nặng như Valgrind. Việc tự viết Custom Allocator (ghi đè malloc/free) ghi lại siêu dữ liệu (metadata) giúp theo dõi bộ nhớ rò rỉ rất hiệu quả.</v>
       </c>
       <c r="E25" t="str">
+        <v>Sử dụng phần mềm Valgrind chạy trực tiếp trên chip vi điều khiển để quét bộ nhớ</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Thường xuyên reset vi điều khiển bằng mạch Watchdog Timer để xóa sạch bộ nhớ RAM</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Đổi toàn bộ con trỏ trong mã nguồn C thành các biến mảng tĩnh có kích thước cố định</v>
+      </c>
+      <c r="H25" t="str">
         <v>Viết lại hàm `malloc()` và `free()` tùy biến (Custom Memory Allocator) để ghi log địa chỉ cấp phát/giải phóng, kiểm tra tính cân bằng của con trỏ, hoặc dùng công cụ phân tích tĩnh (Static Analysis)</v>
       </c>
-      <c r="F25" t="str">
-        <v>Sử dụng phần mềm Valgrind chạy trực tiếp trên chip vi điều khiển để quét bộ nhớ</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Thường xuyên reset vi điều khiển bằng mạch Watchdog Timer để xóa sạch bộ nhớ RAM</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Đổi toàn bộ con trỏ trong mã nguồn C thành các biến mảng tĩnh có kích thước cố định</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1149,10 +1149,10 @@
         <v>Con trỏ hàm (Function Pointer) là kỹ thuật quan trọng trong lập trình nhúng để thiết lập các thư viện Driver phần cứng (ví dụ: đăng ký hàm Callback xử lý khi nhận được byte UART).</v>
       </c>
       <c r="E26" t="str">
+        <v>Khai báo một mảng chứa tối đa 8 phần tử có kiểu dữ liệu là void</v>
+      </c>
+      <c r="F26" t="str">
         <v>Khai báo một kiểu con trỏ hàm nhận tham số 8-bit không dấu; ứng dụng để thiết lập các hàm phản hồi (Callback) xử lý sự kiện ngoại vi động</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Khai báo một mảng chứa tối đa 8 phần tử có kiểu dữ liệu là void</v>
       </c>
       <c r="G26" t="str">
         <v>Khai báo cấu trúc struct ghi đè cơ chế quản lý bộ nhớ của hệ điều hành</v>
@@ -1161,7 +1161,7 @@
         <v>Khai báo một hàm đệ quy tự động giải phóng bộ nhớ Stack khi chạy xong</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
